--- a/data/CodeBook.1.def..xlsx
+++ b/data/CodeBook.1.def..xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennefischer/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennefischer/Travail-de-Master-Etienne-Fischer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FA94CD0-0BD8-4843-BB5A-876F1E3BBA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B460359-C217-4848-97BC-8F94FD2AD62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="15160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extraction" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="312">
   <si>
     <t>Title</t>
   </si>
@@ -341,12 +341,6 @@
     <t>1-2=10%; 3a=14.3%; 3b=16.3%; 4=69.4%</t>
   </si>
   <si>
-    <t>5-years HR 0.68, 95%CI 0.40-1.17,p=0.17</t>
-  </si>
-  <si>
-    <t>5-years HR 0.52, 95%CI 0.29-0.96,p=0.035</t>
-  </si>
-  <si>
     <t>18% &gt;R1; 27/49 used NACR</t>
   </si>
   <si>
@@ -908,15 +902,6 @@
     <t>os_5yr_perc_LR_ITT</t>
   </si>
   <si>
-    <t>rfs_1yr_perc_LR_ITT</t>
-  </si>
-  <si>
-    <t>rfs_3yr_perc_LR_ITT</t>
-  </si>
-  <si>
-    <t>rfs_5yr_perc_LR_ITT</t>
-  </si>
-  <si>
     <t>rfs_5yr_perc_LR_AT</t>
   </si>
   <si>
@@ -962,15 +947,6 @@
     <t>os_5yr_perc_LT_ITT</t>
   </si>
   <si>
-    <t>rfs_1yr_perc_LT_ITT</t>
-  </si>
-  <si>
-    <t>rfs_3yr_perc_LT_ITT</t>
-  </si>
-  <si>
-    <t>rfs_5yr_perc_LT_TT</t>
-  </si>
-  <si>
     <t>OS in KM curves</t>
   </si>
   <si>
@@ -993,13 +969,23 @@
   </si>
   <si>
     <t>1-2=7.73%; 3a=42.5%;3b=42%;4=7.73%</t>
+  </si>
+  <si>
+    <t>1 year HR: 0.63 (0.25-1.59), p= 0.32
+3 years HR: 0.48 (0.26-0.92), p=0.026
+5 years HR: 0.52 (0.29-0.96), p=0.035</t>
+  </si>
+  <si>
+    <t>1-year HR: 0.67 (0.32-1.41), p=0.29
+3-years HR: 0.68 (0.38-1.23), p=0.20
+5-years HR: 0.68 (0.40-1.17), p=0.17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1091,6 +1077,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1484,12 +1477,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1640,9 +1634,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1675,6 +1666,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1685,10 +1691,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Pourcentage" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2047,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A58D03-BA38-474C-A57A-8E3FDED25C33}">
-  <dimension ref="A1:CT13"/>
+  <dimension ref="A1:CN13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2073,55 +2080,53 @@
     <col min="21" max="21" width="19" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="33.5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="19" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="21" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="19" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="21" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="22" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="21" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="22" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="25.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="58" width="19" bestFit="1" customWidth="1"/>
-    <col min="59" max="61" width="21" bestFit="1" customWidth="1"/>
-    <col min="62" max="64" width="19" bestFit="1" customWidth="1"/>
-    <col min="65" max="67" width="21" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="19" style="71" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="21" style="71" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="19" style="71" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="21" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="22" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="53" max="55" width="19" style="71" bestFit="1" customWidth="1"/>
+    <col min="56" max="58" width="21" style="71" bestFit="1" customWidth="1"/>
+    <col min="59" max="61" width="19" style="71" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="33.5" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="22" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="21" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="71" max="71" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="22" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="21" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="54.33203125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="21" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="22" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="53.33203125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="76" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="21" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="22" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="76" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:92" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47"/>
       <c r="B1" s="49" t="s">
         <v>0</v>
@@ -2189,194 +2194,176 @@
       <c r="W1" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="44" t="s">
+      <c r="X1" s="70" t="s">
+        <v>292</v>
+      </c>
+      <c r="Y1" s="70" t="s">
+        <v>291</v>
+      </c>
+      <c r="Z1" s="70" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA1" s="70" t="s">
+        <v>289</v>
+      </c>
+      <c r="AB1" s="70" t="s">
+        <v>288</v>
+      </c>
+      <c r="AC1" s="70" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD1" s="70" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE1" s="70" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF1" s="70" t="s">
+        <v>286</v>
+      </c>
+      <c r="AG1" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU1" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV1" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="AW1" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="AX1" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY1" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="AZ1" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" s="72" t="s">
+        <v>293</v>
+      </c>
+      <c r="BB1" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="BC1" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="BD1" s="72" t="s">
+        <v>296</v>
+      </c>
+      <c r="BE1" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="Y1" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="Z1" s="44" t="s">
-        <v>295</v>
-      </c>
-      <c r="AA1" s="44" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB1" s="44" t="s">
-        <v>293</v>
-      </c>
-      <c r="AC1" s="44" t="s">
-        <v>292</v>
-      </c>
-      <c r="AD1" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="AE1" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="AF1" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="AG1" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="AH1" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="AI1" s="44" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ1" s="44" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK1" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="AL1" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="AM1" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="AN1" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO1" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="AP1" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="AQ1" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR1" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="AS1" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="AT1" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="AU1" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="AV1" s="44" t="s">
-        <v>40</v>
-      </c>
-      <c r="AW1" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX1" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="AY1" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="AZ1" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="BA1" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="BB1" s="45" t="s">
-        <v>46</v>
-      </c>
-      <c r="BC1" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="BD1" s="45" t="s">
+      <c r="BF1" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="BE1" s="45" t="s">
+      <c r="BG1" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="BF1" s="45" t="s">
+      <c r="BH1" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="BG1" s="45" t="s">
+      <c r="BI1" s="72" t="s">
         <v>301</v>
       </c>
-      <c r="BH1" s="45" t="s">
-        <v>302</v>
-      </c>
-      <c r="BI1" s="45" t="s">
-        <v>303</v>
-      </c>
       <c r="BJ1" s="45" t="s">
-        <v>304</v>
+        <v>54</v>
       </c>
       <c r="BK1" s="45" t="s">
-        <v>305</v>
+        <v>55</v>
       </c>
       <c r="BL1" s="45" t="s">
-        <v>306</v>
+        <v>56</v>
       </c>
       <c r="BM1" s="45" t="s">
-        <v>307</v>
+        <v>57</v>
       </c>
       <c r="BN1" s="45" t="s">
-        <v>308</v>
+        <v>58</v>
       </c>
       <c r="BO1" s="45" t="s">
-        <v>309</v>
+        <v>59</v>
       </c>
       <c r="BP1" s="45" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="BQ1" s="45" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="BR1" s="45" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="BS1" s="45" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="BT1" s="45" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="BU1" s="45" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="BV1" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="BW1" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="BX1" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="BY1" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="BZ1" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="CA1" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="CB1" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="CC1" s="46" t="s">
+      <c r="BW1" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="CD1" s="46" t="s">
+      <c r="BX1" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="CE1" s="46" t="s">
+      <c r="BY1" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="CF1" s="46" t="s">
+      <c r="BZ1" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="CG1" s="44" t="s">
+      <c r="CA1" s="44" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:98" s="51" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:92" s="51" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>72</v>
       </c>
@@ -2446,31 +2433,31 @@
       <c r="W2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="X2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="Z2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AB2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2" s="42" t="s">
+      <c r="X2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="52" t="s">
         <v>73</v>
       </c>
       <c r="AG2" s="42" t="s">
@@ -2483,13 +2470,13 @@
         <v>73</v>
       </c>
       <c r="AJ2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AM2" s="42" t="s">
         <v>74</v>
@@ -2513,82 +2500,82 @@
         <v>74</v>
       </c>
       <c r="AT2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="AZ2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BF2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BG2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BH2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BI2" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="BJ2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BK2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BL2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="AU2" s="42" t="s">
+      <c r="BM2" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BN2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="AV2" s="42" t="s">
+      <c r="BO2" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="AW2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AZ2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BA2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BB2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BC2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BD2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BE2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BF2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BG2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BH2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BI2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BJ2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BK2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BL2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BM2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BN2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="BO2" s="42" t="s">
-        <v>73</v>
-      </c>
       <c r="BP2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BQ2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BR2" s="42" t="s">
         <v>74</v>
       </c>
       <c r="BS2" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BT2" s="42" t="s">
         <v>74</v>
@@ -2606,42 +2593,24 @@
         <v>74</v>
       </c>
       <c r="BY2" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="BZ2" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CA2" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CB2" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CC2" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CD2" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CE2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF2" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CG2" s="61"/>
-    </row>
-    <row r="3" spans="1:98" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA2" s="60"/>
+    </row>
+    <row r="3" spans="1:92" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="73" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="55" t="s">
         <v>76</v>
       </c>
       <c r="C3" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="58" t="s">
         <v>78</v>
       </c>
       <c r="E3" s="42" t="s">
@@ -2684,7 +2653,7 @@
       <c r="R3" s="42">
         <v>82</v>
       </c>
-      <c r="S3" s="55" t="s">
+      <c r="S3" s="54" t="s">
         <v>87</v>
       </c>
       <c r="T3" s="42" t="s">
@@ -2699,190 +2668,196 @@
       <c r="W3" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="42"/>
-      <c r="AA3" s="52"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL3" s="42">
+      <c r="X3" s="52">
+        <v>0.753</v>
+      </c>
+      <c r="Y3" s="52">
+        <v>0.217</v>
+      </c>
+      <c r="Z3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA3" s="52">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="AB3" s="52">
+        <v>0.253</v>
+      </c>
+      <c r="AC3" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI3" s="42">
         <v>65.2</v>
       </c>
-      <c r="AM3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN3" s="52">
+      <c r="AJ3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK3" s="52">
         <v>0.13400000000000001</v>
       </c>
-      <c r="AO3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX3" s="42">
+      <c r="AL3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU3" s="42">
         <v>23</v>
       </c>
-      <c r="AY3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AZ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BB3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD3" s="52"/>
-      <c r="BE3" s="52"/>
-      <c r="BF3" s="55"/>
-      <c r="BG3" s="52"/>
-      <c r="BH3" s="52"/>
-      <c r="BI3" s="55"/>
-      <c r="BJ3" s="52"/>
-      <c r="BK3" s="52"/>
-      <c r="BL3" s="55"/>
-      <c r="BM3" s="52"/>
-      <c r="BN3" s="52"/>
-      <c r="BO3" s="55"/>
-      <c r="BP3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BR3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS3" s="42">
+      <c r="AV3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA3" s="64">
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="BB3" s="66">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="BC3" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BD3" s="66">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="BE3" s="66">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="BF3" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI3" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM3" s="42">
         <v>52</v>
       </c>
-      <c r="BT3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BU3" s="53">
+      <c r="BN3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO3" s="53">
         <v>0.87</v>
       </c>
-      <c r="BV3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BX3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE3" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF3" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CG3" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="CH3" s="52">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="CI3" s="52">
-        <v>0.113</v>
-      </c>
-      <c r="CJ3" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CK3" s="52">
-        <v>0.69799999999999995</v>
-      </c>
-      <c r="CL3" s="52">
-        <v>0.24399999999999999</v>
-      </c>
-      <c r="CM3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CO3" s="52">
-        <v>0.91200000000000003</v>
-      </c>
-      <c r="CP3" s="52">
-        <v>0.754</v>
-      </c>
-      <c r="CQ3" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CR3" s="52">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="CS3" s="52">
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="CT3" s="55" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:98" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="68"/>
-      <c r="B4" s="56" t="s">
+      <c r="BP3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BR3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX3" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY3" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ3" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA3" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="CB3" s="67"/>
+      <c r="CC3" s="67"/>
+      <c r="CD3" s="41"/>
+      <c r="CE3" s="67"/>
+      <c r="CF3" s="67"/>
+      <c r="CG3" s="68"/>
+      <c r="CI3" s="67"/>
+      <c r="CJ3" s="67"/>
+      <c r="CK3" s="68"/>
+      <c r="CL3" s="67"/>
+      <c r="CM3" s="67"/>
+      <c r="CN3" s="68"/>
+    </row>
+    <row r="4" spans="1:92" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="74"/>
+      <c r="B4" s="55" t="s">
         <v>88</v>
       </c>
       <c r="C4" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="58" t="s">
         <v>90</v>
       </c>
       <c r="E4" s="42" t="s">
@@ -2923,7 +2898,7 @@
       <c r="R4" s="42">
         <v>60</v>
       </c>
-      <c r="S4" s="55" t="s">
+      <c r="S4" s="54" t="s">
         <v>87</v>
       </c>
       <c r="T4" s="42">
@@ -2938,198 +2913,204 @@
       <c r="W4" s="52">
         <v>0.49199999999999999</v>
       </c>
-      <c r="X4" s="53">
+      <c r="X4" s="52">
         <v>0.65</v>
       </c>
-      <c r="Y4" s="53">
+      <c r="Y4" s="52">
         <v>0.41</v>
       </c>
-      <c r="Z4" s="53">
+      <c r="Z4" s="52">
         <v>0.2</v>
       </c>
-      <c r="AA4" s="53">
+      <c r="AA4" s="52">
         <v>0.72</v>
       </c>
-      <c r="AB4" s="53">
+      <c r="AB4" s="52">
         <v>0.25</v>
       </c>
-      <c r="AC4" s="53">
+      <c r="AC4" s="52">
         <v>0.2</v>
       </c>
-      <c r="AD4" s="53"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="53"/>
-      <c r="AI4" s="53"/>
-      <c r="AJ4" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK4" s="53">
+      <c r="AD4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG4" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH4" s="53">
         <v>0.4</v>
       </c>
-      <c r="AL4" s="42">
+      <c r="AI4" s="42">
         <v>66</v>
       </c>
-      <c r="AM4" s="52">
+      <c r="AJ4" s="52">
         <v>0.68300000000000005</v>
       </c>
-      <c r="AN4" s="52">
+      <c r="AK4" s="52">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="AO4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP4" s="42" t="s">
+      <c r="AL4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM4" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="AQ4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS4" s="55">
+      <c r="AN4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP4" s="54">
         <v>125</v>
       </c>
-      <c r="AT4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV4" s="55">
+      <c r="AQ4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS4" s="54">
         <v>16</v>
       </c>
-      <c r="AW4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX4" s="42">
+      <c r="AT4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU4" s="42">
         <v>49</v>
       </c>
-      <c r="AY4" s="42" t="s">
+      <c r="AV4" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="AZ4" s="42">
+      <c r="AW4" s="42">
         <v>26</v>
       </c>
+      <c r="AX4" s="52">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="AY4" s="52">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AZ4" s="54" t="s">
+        <v>87</v>
+      </c>
       <c r="BA4" s="52">
-        <v>0.32400000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BB4" s="52">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="BC4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD4" s="53">
-        <v>0.76</v>
-      </c>
-      <c r="BE4" s="53">
         <v>0.56000000000000005</v>
       </c>
-      <c r="BF4" s="53">
+      <c r="BC4" s="52">
         <v>0.42</v>
       </c>
-      <c r="BG4" s="53">
+      <c r="BD4" s="52">
         <v>0.81</v>
       </c>
-      <c r="BH4" s="53">
+      <c r="BE4" s="52">
         <v>0.56000000000000005</v>
       </c>
-      <c r="BI4" s="53">
+      <c r="BF4" s="52">
         <v>0.43</v>
       </c>
-      <c r="BJ4" s="53"/>
-      <c r="BK4" s="53"/>
-      <c r="BL4" s="53"/>
-      <c r="BM4" s="53"/>
-      <c r="BN4" s="53"/>
-      <c r="BO4" s="53"/>
-      <c r="BP4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ4" s="52">
+      <c r="BG4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI4" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK4" s="52">
         <v>0.46899999999999997</v>
       </c>
-      <c r="BR4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS4" s="42">
+      <c r="BL4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM4" s="42">
         <v>54</v>
       </c>
-      <c r="BT4" s="52">
+      <c r="BN4" s="52">
         <v>0.69399999999999995</v>
       </c>
-      <c r="BU4" s="52">
+      <c r="BO4" s="52">
         <v>0.28599999999999998</v>
       </c>
-      <c r="BV4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW4" s="42" t="s">
+      <c r="BP4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ4" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="BX4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY4" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ4" s="42">
+      <c r="BR4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS4" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT4" s="42">
         <v>143</v>
       </c>
+      <c r="BU4" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV4" s="42">
+        <v>14</v>
+      </c>
+      <c r="BW4" s="59" t="s">
+        <v>311</v>
+      </c>
+      <c r="BX4" s="59" t="s">
+        <v>310</v>
+      </c>
+      <c r="BY4" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ4" s="42" t="s">
+        <v>73</v>
+      </c>
       <c r="CA4" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB4" s="42">
-        <v>14</v>
-      </c>
-      <c r="CC4" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="CD4" s="42" t="s">
+    </row>
+    <row r="5" spans="1:92" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="74"/>
+      <c r="B5" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="CE4" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF4" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CG4" s="42" t="s">
+      <c r="C5" s="42" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="5" spans="1:98" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="68"/>
-      <c r="B5" s="56" t="s">
+      <c r="D5" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>104</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>106</v>
       </c>
       <c r="F5" s="42"/>
       <c r="G5" s="42" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H5" s="42">
         <v>2007</v>
       </c>
       <c r="I5" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="K5" s="42" t="s">
         <v>108</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="K5" s="42" t="s">
-        <v>110</v>
       </c>
       <c r="L5" s="42"/>
       <c r="M5" s="42">
@@ -3150,7 +3131,7 @@
       <c r="R5" s="42">
         <v>44</v>
       </c>
-      <c r="S5" s="55" t="s">
+      <c r="S5" s="54" t="s">
         <v>87</v>
       </c>
       <c r="T5" s="42">
@@ -3165,184 +3146,190 @@
       <c r="W5" s="53">
         <v>0.36</v>
       </c>
-      <c r="X5" s="53">
+      <c r="X5" s="52">
         <v>0.6</v>
       </c>
-      <c r="Y5" s="53">
+      <c r="Y5" s="52">
         <v>0.43</v>
       </c>
-      <c r="Z5" s="53">
+      <c r="Z5" s="52">
         <v>0.28000000000000003</v>
       </c>
-      <c r="AA5" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB5" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="42"/>
-      <c r="AH5" s="42"/>
-      <c r="AI5" s="55"/>
-      <c r="AJ5" s="52">
+      <c r="AA5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC5" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG5" s="52">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="AK5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL5" s="42">
+      <c r="AH5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI5" s="42">
         <v>54.7</v>
       </c>
-      <c r="AM5" s="53">
+      <c r="AJ5" s="53">
         <v>0.5454</v>
       </c>
-      <c r="AN5" s="52">
+      <c r="AK5" s="52">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="AO5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ5" s="42">
+      <c r="AL5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN5" s="42">
         <v>17</v>
       </c>
-      <c r="AR5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV5" s="42">
+      <c r="AO5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS5" s="42">
         <v>20</v>
       </c>
-      <c r="AW5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX5" s="42">
+      <c r="AT5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU5" s="42">
         <v>12</v>
       </c>
-      <c r="AY5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AZ5" s="42" t="s">
+      <c r="AV5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW5" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="AX5" s="52">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="AY5" s="53">
+        <v>0.25</v>
+      </c>
+      <c r="AZ5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA5" s="52">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BB5" s="67">
+        <v>0.41</v>
+      </c>
+      <c r="BC5" s="52">
+        <v>0.2</v>
+      </c>
+      <c r="BD5" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BE5" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF5" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI5" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM5" s="42">
+        <v>47.7</v>
+      </c>
+      <c r="BN5" s="53">
+        <v>0.66</v>
+      </c>
+      <c r="BO5" s="53">
+        <v>0.33</v>
+      </c>
+      <c r="BP5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BR5" s="42">
+        <v>3</v>
+      </c>
+      <c r="BS5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX5" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY5" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ5" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA5" s="60"/>
+    </row>
+    <row r="6" spans="1:92" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="74"/>
+      <c r="B6" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="BA5" s="52">
-        <v>0.58299999999999996</v>
-      </c>
-      <c r="BB5" s="53">
-        <v>0.25</v>
-      </c>
-      <c r="BC5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD5" s="53">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="BE5" s="54">
-        <v>0.41</v>
-      </c>
-      <c r="BF5" s="53">
-        <v>0.2</v>
-      </c>
-      <c r="BG5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BH5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BJ5" s="53"/>
-      <c r="BK5" s="54"/>
-      <c r="BL5" s="53"/>
-      <c r="BM5" s="55"/>
-      <c r="BN5" s="55"/>
-      <c r="BO5" s="55"/>
-      <c r="BP5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BR5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS5" s="42">
-        <v>47.7</v>
-      </c>
-      <c r="BT5" s="53">
-        <v>0.66</v>
-      </c>
-      <c r="BU5" s="53">
-        <v>0.33</v>
-      </c>
-      <c r="BV5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BX5" s="42">
-        <v>3</v>
-      </c>
-      <c r="BY5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD5" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE5" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF5" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG5" s="61"/>
-    </row>
-    <row r="6" spans="1:98" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="68"/>
-      <c r="B6" s="56" t="s">
+      <c r="D6" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="E6" s="42" t="s">
         <v>113</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>115</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H6" s="42">
         <v>2018</v>
@@ -3351,7 +3338,7 @@
         <v>81</v>
       </c>
       <c r="J6" s="42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K6" s="42" t="s">
         <v>95</v>
@@ -3364,10 +3351,10 @@
         <v>232</v>
       </c>
       <c r="O6" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q6" s="42">
         <v>234</v>
@@ -3376,7 +3363,7 @@
         <v>191</v>
       </c>
       <c r="S6" s="42" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T6" s="42">
         <v>30</v>
@@ -3390,198 +3377,192 @@
       <c r="W6" s="53">
         <v>0.3</v>
       </c>
-      <c r="X6" s="53">
+      <c r="X6" s="52">
         <v>0.71</v>
       </c>
-      <c r="Y6" s="53">
+      <c r="Y6" s="52">
         <v>0.33</v>
       </c>
-      <c r="Z6" s="53">
+      <c r="Z6" s="52">
         <v>0.18</v>
       </c>
-      <c r="AA6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD6" s="53">
+      <c r="AA6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD6" s="52">
         <v>0.66</v>
       </c>
-      <c r="AE6" s="53">
+      <c r="AE6" s="52">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AF6" s="53">
+      <c r="AF6" s="52">
         <v>0.17</v>
       </c>
-      <c r="AG6" s="55"/>
-      <c r="AH6" s="55"/>
-      <c r="AI6" s="55"/>
+      <c r="AG6" s="53">
+        <v>0.08</v>
+      </c>
+      <c r="AH6" s="53">
+        <v>0.45</v>
+      </c>
+      <c r="AI6" s="42">
+        <v>67</v>
+      </c>
       <c r="AJ6" s="53">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="AK6" s="53">
-        <v>0.45</v>
-      </c>
-      <c r="AL6" s="42">
-        <v>67</v>
-      </c>
-      <c r="AM6" s="53">
-        <v>0.59</v>
-      </c>
-      <c r="AN6" s="53">
         <v>0.02</v>
       </c>
-      <c r="AO6" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP6" s="42" t="s">
+      <c r="AL6" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM6" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="AN6" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS6" s="42">
+        <v>11</v>
+      </c>
+      <c r="AT6" s="42">
+        <v>70</v>
+      </c>
+      <c r="AU6" s="42">
+        <v>41</v>
+      </c>
+      <c r="AV6" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="AW6" s="42">
+        <v>25</v>
+      </c>
+      <c r="AX6" s="53">
+        <v>0.19</v>
+      </c>
+      <c r="AY6" s="53">
+        <v>0.1</v>
+      </c>
+      <c r="AZ6" s="52">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="BA6" s="52">
+        <v>0.93</v>
+      </c>
+      <c r="BB6" s="52">
+        <v>0.72</v>
+      </c>
+      <c r="BC6" s="52">
+        <v>0.64</v>
+      </c>
+      <c r="BD6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BE6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF6" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG6" s="52">
+        <v>0.8</v>
+      </c>
+      <c r="BH6" s="52">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="BI6" s="52">
+        <v>0.53</v>
+      </c>
+      <c r="BJ6" s="53">
+        <v>0.05</v>
+      </c>
+      <c r="BK6" s="53">
+        <v>0.34</v>
+      </c>
+      <c r="BL6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM6" s="42">
+        <v>54</v>
+      </c>
+      <c r="BN6" s="53">
+        <v>0.71</v>
+      </c>
+      <c r="BO6" s="53">
+        <v>0.61</v>
+      </c>
+      <c r="BP6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ6" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="AQ6" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV6" s="42">
-        <v>11</v>
-      </c>
-      <c r="AW6" s="42">
-        <v>70</v>
-      </c>
-      <c r="AX6" s="42">
-        <v>41</v>
-      </c>
-      <c r="AY6" s="42" t="s">
+      <c r="BR6" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS6" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT6" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU6" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV6" s="42">
+        <v>8</v>
+      </c>
+      <c r="BW6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX6" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY6" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ6" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA6" s="65" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:92" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7" s="74"/>
+      <c r="B7" s="55" t="s">
         <v>122</v>
       </c>
-      <c r="AZ6" s="42">
-        <v>25</v>
-      </c>
-      <c r="BA6" s="53">
-        <v>0.19</v>
-      </c>
-      <c r="BB6" s="53">
-        <v>0.1</v>
-      </c>
-      <c r="BC6" s="52">
-        <v>0.34300000000000003</v>
-      </c>
-      <c r="BD6" s="53">
-        <v>0.93</v>
-      </c>
-      <c r="BE6" s="53">
-        <v>0.72</v>
-      </c>
-      <c r="BF6" s="53">
-        <v>0.64</v>
-      </c>
-      <c r="BG6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BH6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BJ6" s="53">
-        <v>0.8</v>
-      </c>
-      <c r="BK6" s="53">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="BL6" s="53">
-        <v>0.53</v>
-      </c>
-      <c r="BM6" s="55"/>
-      <c r="BN6" s="55"/>
-      <c r="BO6" s="55"/>
-      <c r="BP6" s="53">
-        <v>0.05</v>
-      </c>
-      <c r="BQ6" s="53">
-        <v>0.34</v>
-      </c>
-      <c r="BR6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS6" s="42">
-        <v>54</v>
-      </c>
-      <c r="BT6" s="53">
-        <v>0.71</v>
-      </c>
-      <c r="BU6" s="53">
-        <v>0.61</v>
-      </c>
-      <c r="BV6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW6" s="55" t="s">
+      <c r="C7" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="BX6" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY6" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ6" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA6" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB6" s="42">
-        <v>8</v>
-      </c>
-      <c r="CC6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD6" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE6" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF6" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG6" s="66" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:98" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="68"/>
-      <c r="B7" s="56" t="s">
+      <c r="D7" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="E7" s="42" t="s">
         <v>125</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>127</v>
       </c>
       <c r="F7" s="42"/>
       <c r="G7" s="42" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H7" s="42">
         <v>2025</v>
@@ -3590,13 +3571,13 @@
         <v>81</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K7" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="L7" s="60" t="s">
-        <v>130</v>
+      <c r="L7" s="59" t="s">
+        <v>128</v>
       </c>
       <c r="M7" s="42">
         <v>415</v>
@@ -3605,10 +3586,10 @@
         <v>282</v>
       </c>
       <c r="O7" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="P7" s="60" t="s">
-        <v>275</v>
+        <v>116</v>
+      </c>
+      <c r="P7" s="59" t="s">
+        <v>273</v>
       </c>
       <c r="Q7" s="42">
         <v>288</v>
@@ -3616,7 +3597,7 @@
       <c r="R7" s="42">
         <v>207</v>
       </c>
-      <c r="S7" s="55" t="s">
+      <c r="S7" s="54" t="s">
         <v>87</v>
       </c>
       <c r="T7" s="42">
@@ -3631,176 +3612,192 @@
       <c r="W7" s="52">
         <v>0.19800000000000001</v>
       </c>
-      <c r="X7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="52"/>
-      <c r="AF7" s="52"/>
-      <c r="AG7" s="52"/>
-      <c r="AH7" s="52"/>
-      <c r="AI7" s="52"/>
-      <c r="AJ7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK7" s="52">
+      <c r="X7" s="52">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="Y7" s="52">
+        <v>0.6</v>
+      </c>
+      <c r="Z7" s="52">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="AA7" s="52">
+        <v>0.746</v>
+      </c>
+      <c r="AB7" s="52">
+        <v>0.439</v>
+      </c>
+      <c r="AC7" s="52">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="AD7" s="52">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="AE7" s="52">
+        <v>0.46200000000000002</v>
+      </c>
+      <c r="AF7" s="52">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="AG7" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH7" s="52">
         <v>0.39100000000000001</v>
       </c>
-      <c r="AL7" s="42">
+      <c r="AI7" s="42">
         <v>64</v>
       </c>
-      <c r="AM7" s="52">
+      <c r="AJ7" s="52">
         <v>0.61339999999999995</v>
       </c>
-      <c r="AN7" s="42">
+      <c r="AK7" s="42">
         <v>0</v>
       </c>
-      <c r="AO7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP7" s="42" t="s">
-        <v>317</v>
-      </c>
-      <c r="AQ7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS7" s="42">
+      <c r="AL7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM7" s="42" t="s">
+        <v>309</v>
+      </c>
+      <c r="AN7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP7" s="42">
         <v>76</v>
       </c>
-      <c r="AT7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV7" s="65" t="s">
-        <v>87</v>
+      <c r="AQ7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT7" s="42">
+        <v>127</v>
+      </c>
+      <c r="AU7" s="42">
+        <v>75</v>
+      </c>
+      <c r="AV7" s="42" t="s">
+        <v>120</v>
       </c>
       <c r="AW7" s="42">
-        <v>127</v>
-      </c>
-      <c r="AX7" s="42">
-        <v>75</v>
-      </c>
-      <c r="AY7" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ7" s="42">
         <v>17</v>
       </c>
-      <c r="BA7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="BB7" s="65" t="s">
-        <v>87</v>
+      <c r="AX7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ7" s="52">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="BA7" s="52">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="BB7" s="52">
+        <v>0.80200000000000005</v>
       </c>
       <c r="BC7" s="52">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="BD7" s="52"/>
-      <c r="BE7" s="52"/>
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="BD7" s="52">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="BE7" s="52">
+        <v>0.55600000000000005</v>
+      </c>
       <c r="BF7" s="52">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="BG7" s="52"/>
-      <c r="BH7" s="52"/>
-      <c r="BI7" s="52"/>
-      <c r="BJ7" s="52"/>
-      <c r="BK7" s="52"/>
-      <c r="BL7" s="52"/>
-      <c r="BM7" s="52"/>
-      <c r="BN7" s="52"/>
-      <c r="BO7" s="52"/>
-      <c r="BP7" s="52" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ7" s="53">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="BG7" s="52">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="BH7" s="52">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="BI7" s="52">
+        <v>0.378</v>
+      </c>
+      <c r="BJ7" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK7" s="53">
         <v>0.44</v>
       </c>
-      <c r="BR7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS7" s="42">
+      <c r="BL7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM7" s="42">
         <v>56</v>
       </c>
-      <c r="BT7" s="52">
+      <c r="BN7" s="52">
         <v>0.73299999999999998</v>
       </c>
-      <c r="BU7" s="52">
+      <c r="BO7" s="52">
         <v>0</v>
       </c>
-      <c r="BV7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="BX7" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ7" s="42">
+      <c r="BP7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BR7" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT7" s="42">
         <v>143</v>
       </c>
-      <c r="CA7" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD7" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE7" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF7" s="42" t="s">
+      <c r="BU7" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX7" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY7" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ7" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="CG7" s="42" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="8" spans="1:98" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="68"/>
-      <c r="B8" s="56" t="s">
+      <c r="CA7" s="42" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:92" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="74"/>
+      <c r="B8" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>133</v>
-      </c>
       <c r="E8" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F8" s="42"/>
       <c r="G8" s="42" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H8" s="42">
         <v>2022</v>
@@ -3809,10 +3806,10 @@
         <v>93</v>
       </c>
       <c r="J8" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="60" t="s">
-        <v>277</v>
+        <v>132</v>
+      </c>
+      <c r="K8" s="59" t="s">
+        <v>275</v>
       </c>
       <c r="L8" s="42"/>
       <c r="M8" s="42">
@@ -3842,190 +3839,196 @@
       <c r="U8" s="53">
         <v>0</v>
       </c>
-      <c r="V8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="W8" s="64">
+      <c r="V8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="W8" s="63">
         <v>0.06</v>
       </c>
-      <c r="X8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y8" s="55" t="s">
-        <v>87</v>
+      <c r="X8" s="64">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="Y8" s="64">
+        <v>0.629</v>
       </c>
       <c r="Z8" s="52">
         <v>0.39900000000000002</v>
       </c>
-      <c r="AA8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB8" s="55" t="s">
-        <v>87</v>
+      <c r="AA8" s="64">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="AB8" s="64">
+        <v>0.29299999999999998</v>
       </c>
       <c r="AC8" s="52">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="55"/>
-      <c r="AH8" s="55"/>
-      <c r="AI8" s="52"/>
-      <c r="AJ8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK8" s="52">
+      <c r="AD8" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE8" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF8" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH8" s="52">
         <v>0.746</v>
       </c>
-      <c r="AL8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP8" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="AQ8" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX8" s="42">
+      <c r="AI8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM8" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="AN8" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU8" s="42">
         <v>120</v>
       </c>
-      <c r="AY8" s="42" t="s">
+      <c r="AV8" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX8" s="53">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="52">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AZ8" s="53">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="BA8" s="52">
+        <v>0.91</v>
+      </c>
+      <c r="BB8" s="52">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="BC8" s="52">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="BD8" s="52">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="BE8" s="64">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="BF8" s="52">
+        <v>0.502</v>
+      </c>
+      <c r="BG8" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH8" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI8" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK8" s="52">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="BL8" s="59" t="s">
+        <v>277</v>
+      </c>
+      <c r="BM8" s="42">
+        <v>51</v>
+      </c>
+      <c r="BN8" s="53">
+        <v>0.7</v>
+      </c>
+      <c r="BO8" s="52">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="BP8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ8" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="BR8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU8" s="54">
+        <v>390</v>
+      </c>
+      <c r="BV8" s="42">
+        <v>7</v>
+      </c>
+      <c r="BW8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX8" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY8" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ8" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="CA8" s="42"/>
+    </row>
+    <row r="9" spans="1:92" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="74"/>
+      <c r="B9" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="AZ8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA8" s="53">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="52">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="BC8" s="53">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="BD8" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BE8" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BF8" s="52">
-        <v>0.56299999999999994</v>
-      </c>
-      <c r="BG8" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BH8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI8" s="52">
-        <v>0.502</v>
-      </c>
-      <c r="BJ8" s="42"/>
-      <c r="BK8" s="42"/>
-      <c r="BL8" s="52"/>
-      <c r="BM8" s="42"/>
-      <c r="BN8" s="55"/>
-      <c r="BO8" s="52"/>
-      <c r="BP8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ8" s="52">
-        <v>0.72699999999999998</v>
-      </c>
-      <c r="BR8" s="60" t="s">
-        <v>279</v>
-      </c>
-      <c r="BS8" s="42">
-        <v>51</v>
-      </c>
-      <c r="BT8" s="53">
-        <v>0.7</v>
-      </c>
-      <c r="BU8" s="52">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="BV8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW8" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="BX8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA8" s="55">
-        <v>390</v>
-      </c>
-      <c r="CB8" s="42">
-        <v>7</v>
-      </c>
-      <c r="CC8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD8" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE8" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF8" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CG8" s="42"/>
-    </row>
-    <row r="9" spans="1:98" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="68"/>
-      <c r="B9" s="56" t="s">
+      <c r="D9" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="E9" s="42" t="s">
         <v>138</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>140</v>
       </c>
       <c r="F9" s="42"/>
       <c r="G9" s="42" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H9" s="42">
         <v>2015</v>
@@ -4034,10 +4037,10 @@
         <v>81</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K9" s="42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L9" s="42"/>
       <c r="M9" s="42">
@@ -4047,10 +4050,10 @@
         <v>153</v>
       </c>
       <c r="O9" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P9" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q9" s="42">
         <v>142</v>
@@ -4073,186 +4076,192 @@
       <c r="W9" s="53">
         <v>0.08</v>
       </c>
-      <c r="X9" s="53">
+      <c r="X9" s="52">
         <v>0.81</v>
       </c>
-      <c r="Y9" s="53">
+      <c r="Y9" s="52">
         <v>0.53</v>
       </c>
-      <c r="Z9" s="53">
+      <c r="Z9" s="52">
         <v>0.36</v>
       </c>
-      <c r="AA9" s="53">
+      <c r="AA9" s="52">
         <v>0.74</v>
       </c>
-      <c r="AB9" s="53">
+      <c r="AB9" s="52">
         <v>0.48</v>
       </c>
-      <c r="AC9" s="53">
+      <c r="AC9" s="52">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AD9" s="53"/>
-      <c r="AE9" s="53"/>
-      <c r="AF9" s="53"/>
-      <c r="AG9" s="53"/>
-      <c r="AH9" s="53"/>
-      <c r="AI9" s="53"/>
-      <c r="AJ9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL9" s="42">
+      <c r="AD9" s="69">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="AE9" s="52">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="AF9" s="52">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="AG9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI9" s="42">
         <v>63.3</v>
       </c>
-      <c r="AM9" s="53">
+      <c r="AJ9" s="53">
         <v>0.65</v>
       </c>
-      <c r="AN9" s="42">
+      <c r="AK9" s="42">
         <v>0</v>
       </c>
-      <c r="AO9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP9" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV9" s="55" t="s">
-        <v>87</v>
+      <c r="AL9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM9" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="AN9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT9" s="42">
+        <v>90</v>
+      </c>
+      <c r="AU9" s="42">
+        <v>54</v>
+      </c>
+      <c r="AV9" s="42" t="s">
+        <v>120</v>
       </c>
       <c r="AW9" s="42">
-        <v>90</v>
-      </c>
-      <c r="AX9" s="42">
-        <v>54</v>
-      </c>
-      <c r="AY9" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ9" s="42">
         <v>10</v>
       </c>
-      <c r="BA9" s="53">
+      <c r="AX9" s="53">
         <v>0.02</v>
       </c>
-      <c r="BB9" s="53">
+      <c r="AY9" s="53">
         <v>0</v>
       </c>
-      <c r="BC9" s="53">
+      <c r="AZ9" s="53">
         <v>0.4</v>
       </c>
-      <c r="BD9" s="53">
+      <c r="BA9" s="52">
         <v>0.9</v>
       </c>
-      <c r="BE9" s="53">
+      <c r="BB9" s="52">
         <v>0.71</v>
       </c>
-      <c r="BF9" s="53">
+      <c r="BC9" s="52">
         <v>0.59</v>
       </c>
-      <c r="BG9" s="53">
+      <c r="BD9" s="52">
         <v>0.87</v>
       </c>
-      <c r="BH9" s="53">
+      <c r="BE9" s="52">
         <v>0.64</v>
       </c>
-      <c r="BI9" s="53">
+      <c r="BF9" s="52">
         <v>0.54</v>
       </c>
-      <c r="BJ9" s="53"/>
-      <c r="BK9" s="53"/>
-      <c r="BL9" s="53"/>
-      <c r="BM9" s="53"/>
-      <c r="BN9" s="53"/>
-      <c r="BO9" s="53"/>
-      <c r="BP9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BR9" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="BS9" s="42">
+      <c r="BG9" s="52">
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="BH9" s="52">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="BI9" s="52">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="BJ9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL9" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="BM9" s="42">
         <v>54.1</v>
       </c>
-      <c r="BT9" s="53">
+      <c r="BN9" s="53">
         <v>0.74</v>
       </c>
-      <c r="BU9" s="42">
+      <c r="BO9" s="42">
         <v>0</v>
       </c>
-      <c r="BV9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW9" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="BX9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD9" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE9" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF9" s="42" t="s">
+      <c r="BP9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ9" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="BR9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX9" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY9" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ9" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="CG9" s="66" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:98" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="68"/>
-      <c r="B10" s="56" t="s">
+      <c r="CA9" s="65" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:92" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="74"/>
+      <c r="B10" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="58" t="s">
         <v>144</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>146</v>
-      </c>
       <c r="E10" s="42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H10" s="42">
         <v>1998</v>
@@ -4261,10 +4270,10 @@
         <v>81</v>
       </c>
       <c r="J10" s="42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L10" s="42"/>
       <c r="M10" s="41">
@@ -4279,16 +4288,16 @@
       <c r="P10" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="Q10" s="55" t="s">
+      <c r="Q10" s="54" t="s">
         <v>87</v>
       </c>
       <c r="R10" s="42">
         <v>34</v>
       </c>
       <c r="S10" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="T10" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="T10" s="54" t="s">
         <v>87</v>
       </c>
       <c r="U10" s="53">
@@ -4309,188 +4318,194 @@
       <c r="Z10" s="52">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="AA10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="52"/>
-      <c r="AF10" s="52"/>
-      <c r="AG10" s="55"/>
-      <c r="AH10" s="55"/>
-      <c r="AI10" s="55"/>
-      <c r="AJ10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM10" s="52">
+      <c r="AA10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE10" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF10" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ10" s="52">
         <v>0.52900000000000003</v>
       </c>
-      <c r="AN10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW10" s="42">
+      <c r="AK10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT10" s="42">
         <v>27</v>
       </c>
-      <c r="AX10" s="42">
+      <c r="AU10" s="42">
         <v>27</v>
       </c>
-      <c r="AY10" s="42" t="s">
-        <v>284</v>
-      </c>
-      <c r="AZ10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA10" s="53">
+      <c r="AV10" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="AW10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX10" s="53">
         <v>0.22</v>
       </c>
-      <c r="BB10" s="53">
+      <c r="AY10" s="53">
         <v>0.22</v>
       </c>
-      <c r="BC10" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD10" s="52">
+      <c r="AZ10" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA10" s="52">
         <v>0.59299999999999997</v>
       </c>
-      <c r="BE10" s="52">
+      <c r="BB10" s="52">
         <v>0.36199999999999999</v>
       </c>
-      <c r="BF10" s="52">
+      <c r="BC10" s="52">
         <v>0.36199999999999999</v>
       </c>
-      <c r="BG10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BH10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BJ10" s="52"/>
-      <c r="BK10" s="52"/>
-      <c r="BL10" s="52"/>
-      <c r="BM10" s="55"/>
-      <c r="BN10" s="55"/>
-      <c r="BO10" s="55"/>
-      <c r="BP10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BQ10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BR10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BT10" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BU10" s="52">
+      <c r="BD10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BE10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG10" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH10" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI10" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BK10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN10" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO10" s="52">
         <v>0.48180000000000001</v>
       </c>
-      <c r="BV10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BX10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BY10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD10" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE10" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF10" s="42" t="s">
+      <c r="BP10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BR10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BS10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BU10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX10" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY10" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ10" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="CG10" s="61"/>
-      <c r="CH10" s="62"/>
-    </row>
-    <row r="11" spans="1:98" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="68"/>
-      <c r="B11" s="56" t="s">
+      <c r="CA10" s="60"/>
+      <c r="CB10" s="61"/>
+    </row>
+    <row r="11" spans="1:92" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="74"/>
+      <c r="B11" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="E11" s="42" t="s">
         <v>152</v>
-      </c>
-      <c r="D11" s="59" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>154</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H11" s="42">
         <v>2010</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L11" s="42"/>
       <c r="M11" s="42">
@@ -4512,7 +4527,7 @@
         <v>29</v>
       </c>
       <c r="S11" s="42" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="T11" s="42" t="s">
         <v>87</v>
@@ -4526,196 +4541,202 @@
       <c r="W11" s="53">
         <v>0.17</v>
       </c>
-      <c r="X11" s="53">
-        <v>0.8</v>
-      </c>
-      <c r="Y11" s="53">
-        <v>0.52</v>
-      </c>
-      <c r="Z11" s="53">
-        <v>0.36</v>
-      </c>
-      <c r="AA11" s="53">
+      <c r="X11" s="52">
+        <v>0.85</v>
+      </c>
+      <c r="Y11" s="52">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="Z11" s="52">
+        <v>0.432</v>
+      </c>
+      <c r="AA11" s="52">
         <v>0.65</v>
       </c>
-      <c r="AB11" s="53">
+      <c r="AB11" s="52">
         <v>0.35</v>
       </c>
-      <c r="AC11" s="53">
+      <c r="AC11" s="52">
         <v>0.19</v>
       </c>
-      <c r="AD11" s="53"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="53"/>
-      <c r="AG11" s="53"/>
-      <c r="AH11" s="53"/>
-      <c r="AI11" s="53"/>
-      <c r="AJ11" s="52">
+      <c r="AD11" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE11" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF11" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG11" s="52">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="AK11" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL11" s="42">
+      <c r="AH11" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI11" s="42">
         <v>64</v>
       </c>
-      <c r="AM11" s="53">
+      <c r="AJ11" s="53">
         <v>0.48</v>
       </c>
-      <c r="AN11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP11" s="55" t="s">
+      <c r="AK11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM11" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="AN11" s="53">
+        <v>0.17</v>
+      </c>
+      <c r="AO11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP11" s="42">
+        <v>382</v>
+      </c>
+      <c r="AQ11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT11" s="42">
+        <v>11</v>
+      </c>
+      <c r="AU11" s="42">
+        <v>11</v>
+      </c>
+      <c r="AV11" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="AW11" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX11" s="53">
+        <v>0.18</v>
+      </c>
+      <c r="AY11" s="53">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="53">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="52">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="BB11" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="BC11" s="52">
+        <v>0.5</v>
+      </c>
+      <c r="BD11" s="52">
+        <v>0.75</v>
+      </c>
+      <c r="BE11" s="52">
+        <v>0.4</v>
+      </c>
+      <c r="BF11" s="52">
+        <v>0.2</v>
+      </c>
+      <c r="BG11" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH11" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI11" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ11" s="53">
+        <v>0</v>
+      </c>
+      <c r="BK11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM11" s="42">
+        <v>51</v>
+      </c>
+      <c r="BN11" s="53">
+        <v>0.91</v>
+      </c>
+      <c r="BO11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BQ11" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="BR11" s="42">
+        <v>1</v>
+      </c>
+      <c r="BS11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT11" s="42">
+        <v>371</v>
+      </c>
+      <c r="BU11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BV11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BW11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BX11" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY11" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="BZ11" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="CA11" s="60"/>
+    </row>
+    <row r="12" spans="1:92" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="75"/>
+      <c r="B12" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="AQ11" s="53">
-        <v>0.17</v>
-      </c>
-      <c r="AR11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS11" s="42">
-        <v>382</v>
-      </c>
-      <c r="AT11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW11" s="42">
-        <v>11</v>
-      </c>
-      <c r="AX11" s="42">
-        <v>11</v>
-      </c>
-      <c r="AY11" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="AZ11" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA11" s="53">
-        <v>0.18</v>
-      </c>
-      <c r="BB11" s="53">
-        <v>0</v>
-      </c>
-      <c r="BC11" s="53">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="53">
-        <v>0.95</v>
-      </c>
-      <c r="BE11" s="53">
-        <v>0.59</v>
-      </c>
-      <c r="BF11" s="53">
-        <v>0.36</v>
-      </c>
-      <c r="BG11" s="53">
-        <v>0.75</v>
-      </c>
-      <c r="BH11" s="53">
-        <v>0.4</v>
-      </c>
-      <c r="BI11" s="53">
-        <v>0.2</v>
-      </c>
-      <c r="BJ11" s="53"/>
-      <c r="BK11" s="53"/>
-      <c r="BL11" s="53"/>
-      <c r="BM11" s="53"/>
-      <c r="BN11" s="53"/>
-      <c r="BO11" s="53"/>
-      <c r="BP11" s="53">
-        <v>0</v>
-      </c>
-      <c r="BQ11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BR11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BS11" s="42">
-        <v>51</v>
-      </c>
-      <c r="BT11" s="53">
-        <v>0.91</v>
-      </c>
-      <c r="BU11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BV11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BW11" s="42" t="s">
+      <c r="C12" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="BX11" s="42">
-        <v>1</v>
-      </c>
-      <c r="BY11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="BZ11" s="42">
-        <v>371</v>
-      </c>
-      <c r="CA11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE11" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF11" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG11" s="61"/>
-    </row>
-    <row r="12" spans="1:98" ht="33" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="69"/>
-      <c r="B12" s="56" t="s">
+      <c r="D12" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" s="59" t="s">
-        <v>160</v>
-      </c>
       <c r="E12" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F12" s="42"/>
       <c r="G12" s="42" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H12" s="42">
         <v>1996</v>
       </c>
       <c r="I12" s="42" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K12" s="42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L12" s="42"/>
       <c r="M12" s="42">
@@ -4751,7 +4772,7 @@
       <c r="W12" s="52">
         <v>0.216</v>
       </c>
-      <c r="X12" s="53">
+      <c r="X12" s="52">
         <v>0.65</v>
       </c>
       <c r="Y12" s="52">
@@ -4760,24 +4781,36 @@
       <c r="Z12" s="52">
         <v>0.27100000000000002</v>
       </c>
-      <c r="AA12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD12" s="53"/>
-      <c r="AE12" s="52"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="42"/>
-      <c r="AH12" s="42"/>
-      <c r="AI12" s="42"/>
-      <c r="AJ12" s="52">
+      <c r="AA12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD12" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE12" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF12" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG12" s="52">
         <v>0.105</v>
       </c>
+      <c r="AH12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" s="42" t="s">
+        <v>87</v>
+      </c>
       <c r="AK12" s="42" t="s">
         <v>87</v>
       </c>
@@ -4790,78 +4823,90 @@
       <c r="AN12" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="AO12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR12" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AS12" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT12" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AU12" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV12" s="55" t="s">
+      <c r="AO12" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP12" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ12" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AR12" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS12" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU12" s="42">
+        <v>25</v>
+      </c>
+      <c r="AV12" s="42" t="s">
         <v>87</v>
       </c>
       <c r="AW12" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="AX12" s="42">
-        <v>25</v>
+      <c r="AX12" s="53">
+        <v>0.32</v>
       </c>
       <c r="AY12" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="AZ12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BA12" s="53">
-        <v>0.32</v>
-      </c>
-      <c r="BB12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BC12" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="BD12" s="53">
+      <c r="AZ12" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA12" s="52">
         <v>0.6</v>
       </c>
-      <c r="BE12" s="52">
+      <c r="BB12" s="52">
         <v>0.214</v>
       </c>
-      <c r="BF12" s="52">
+      <c r="BC12" s="52">
         <v>0.17100000000000001</v>
       </c>
-      <c r="BG12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BH12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BI12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="BJ12" s="53"/>
-      <c r="BK12" s="52"/>
-      <c r="BL12" s="52"/>
-      <c r="BM12" s="42"/>
-      <c r="BN12" s="42"/>
-      <c r="BO12" s="42"/>
-      <c r="BP12" s="53">
+      <c r="BD12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BE12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF12" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="BG12" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH12" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BI12" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="BJ12" s="53">
         <v>0.12</v>
       </c>
+      <c r="BK12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BL12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BM12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BN12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO12" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="BP12" s="42" t="s">
+        <v>87</v>
+      </c>
       <c r="BQ12" s="42" t="s">
         <v>87</v>
       </c>
@@ -4887,34 +4932,16 @@
         <v>87</v>
       </c>
       <c r="BY12" s="42" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="BZ12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CA12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CB12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CC12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CD12" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="CE12" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="CF12" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="CG12" s="66" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:98" x14ac:dyDescent="0.2">
+      <c r="CA12" s="65" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:92" x14ac:dyDescent="0.2">
       <c r="O13" s="41"/>
       <c r="P13" s="41"/>
       <c r="Q13" s="41"/>
@@ -4924,15 +4951,15 @@
       <c r="U13" s="41"/>
       <c r="V13" s="41"/>
       <c r="W13" s="41"/>
-      <c r="X13" s="41"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="41"/>
-      <c r="AA13" s="41"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="41"/>
-      <c r="AD13" s="41"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="41"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="67"/>
+      <c r="Z13" s="67"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="67"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="67"/>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67"/>
       <c r="AG13" s="41"/>
       <c r="AH13" s="41"/>
       <c r="AI13" s="41"/>
@@ -4953,15 +4980,15 @@
       <c r="AX13" s="41"/>
       <c r="AY13" s="41"/>
       <c r="AZ13" s="41"/>
-      <c r="BA13" s="41"/>
-      <c r="BB13" s="41"/>
-      <c r="BC13" s="41"/>
-      <c r="BD13" s="41"/>
-      <c r="BE13" s="41"/>
-      <c r="BF13" s="41"/>
-      <c r="BG13" s="41"/>
-      <c r="BH13" s="41"/>
-      <c r="BI13" s="41"/>
+      <c r="BA13" s="67"/>
+      <c r="BB13" s="67"/>
+      <c r="BC13" s="67"/>
+      <c r="BD13" s="67"/>
+      <c r="BE13" s="67"/>
+      <c r="BF13" s="67"/>
+      <c r="BG13" s="67"/>
+      <c r="BH13" s="67"/>
+      <c r="BI13" s="67"/>
       <c r="BJ13" s="41"/>
       <c r="BK13" s="41"/>
       <c r="BL13" s="41"/>
@@ -4980,23 +5007,18 @@
       <c r="BY13" s="41"/>
       <c r="BZ13" s="41"/>
       <c r="CA13" s="41"/>
-      <c r="CB13" s="41"/>
-      <c r="CC13" s="41"/>
-      <c r="CD13" s="41"/>
-      <c r="CE13" s="41"/>
-      <c r="CF13" s="41"/>
-      <c r="CG13" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:A12"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:CF2">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="A2:BZ2">
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:CG2 BC12 B13:CG13">
+  <conditionalFormatting sqref="A2:CA2 AZ12 B13:CA13">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",A2)))</formula>
     </cfRule>
@@ -5064,13 +5086,13 @@
   <sheetData>
     <row r="1" spans="1:45" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>165</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -5117,13 +5139,13 @@
     </row>
     <row r="2" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="31" t="s">
         <v>166</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5170,13 +5192,13 @@
     </row>
     <row r="3" spans="1:45" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>169</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5184,10 +5206,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -5237,10 +5259,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5290,7 +5312,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C6" s="26"/>
     </row>
@@ -5299,10 +5321,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5310,10 +5332,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5321,10 +5343,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5332,10 +5354,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5343,10 +5365,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5354,10 +5376,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5365,10 +5387,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5376,10 +5398,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="16" x14ac:dyDescent="0.2">
@@ -5387,10 +5409,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -5398,10 +5420,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5409,10 +5431,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5420,10 +5442,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5431,21 +5453,21 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="26" t="s">
         <v>199</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5453,10 +5475,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5464,21 +5486,21 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>205</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5486,10 +5508,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5497,10 +5519,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5508,10 +5530,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5519,10 +5541,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5530,10 +5552,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5541,10 +5563,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5552,10 +5574,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5563,10 +5585,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5574,10 +5596,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5585,21 +5607,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C34" s="26" t="s">
         <v>223</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5607,10 +5629,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5618,10 +5640,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5629,21 +5651,21 @@
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="C38" s="24" t="s">
         <v>231</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5651,10 +5673,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5662,10 +5684,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5673,10 +5695,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -5684,10 +5706,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5695,10 +5717,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C43" s="27" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5706,21 +5728,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C45" s="26" t="s">
         <v>245</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5728,21 +5750,21 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5750,10 +5772,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5761,10 +5783,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5772,10 +5794,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5783,10 +5805,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5794,10 +5816,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5805,10 +5827,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5816,10 +5838,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5827,10 +5849,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5838,21 +5860,21 @@
         <v>55</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C57" s="26" t="s">
         <v>260</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5860,10 +5882,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5871,10 +5893,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5882,10 +5904,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5893,10 +5915,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5904,10 +5926,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5915,10 +5937,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5926,10 +5948,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5937,10 +5959,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5948,10 +5970,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -5959,10 +5981,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5970,10 +5992,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C68" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -5981,30 +6003,30 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C69" s="26"/>
     </row>
     <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="38" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="39" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
